--- a/data/return_tasks.xlsx
+++ b/data/return_tasks.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>OD337960018546</t>
+          <t>OD337960018546978100</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>OD337915105120</t>
+          <t>OD337915105120141100</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>OD337915012166</t>
+          <t>OD337915012166989100</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>OD337983703007</t>
+          <t>OD337983703007211100</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>OD337974610559</t>
+          <t>OD337974610559997100</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>OD337974610559</t>
+          <t>OD337974610559997100</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>OD337974610559</t>
+          <t>OD337974610559997100</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>OD337974610559</t>
+          <t>OD337974610559997100</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
